--- a/jira_export_2026-10-15.xlsx
+++ b/jira_export_2026-10-15.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>234 h</t>
+          <t>241 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P154"/>
+  <dimension ref="A1:P155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1821,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L16" s="14" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
@@ -6558,32 +6558,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
@@ -6605,22 +6605,22 @@
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>680.8</v>
-      </c>
-      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6630,12 +6630,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
@@ -6681,16 +6681,16 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6702,32 +6702,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6753,16 +6753,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>403.074</v>
+        <v>2614.5</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6774,32 +6774,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -6825,19 +6825,19 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
-        <v>276</v>
+        <v>403.074</v>
+      </c>
+      <c r="O85" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
         <v>0</v>
@@ -6846,32 +6846,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
@@ -6897,19 +6897,19 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O86" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
+        <v>276</v>
       </c>
       <c r="P86" s="15" t="n">
         <v>0</v>
@@ -6918,32 +6918,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6953,32 +6953,32 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>11278.05</v>
+        <v>142.1</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6990,32 +6990,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
@@ -7041,16 +7041,16 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>1000</v>
+        <v>11278.05</v>
       </c>
       <c r="O88" s="16" t="n">
         <v>0</v>
@@ -7062,32 +7062,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -7113,16 +7113,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7134,12 +7134,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
@@ -7185,16 +7185,16 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O90" s="16" t="n">
         <v>0</v>
@@ -7206,32 +7206,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7241,32 +7241,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7278,32 +7278,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7313,32 +7313,32 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>3240</v>
+        <v>910</v>
       </c>
       <c r="O92" s="16" t="n">
         <v>0</v>
@@ -7350,27 +7350,27 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
@@ -7401,16 +7401,16 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>1050</v>
+        <v>3240</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7422,27 +7422,27 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
@@ -7473,16 +7473,16 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O94" s="16" t="n">
         <v>0</v>
@@ -7494,32 +7494,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7529,34 +7529,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7566,32 +7566,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7601,34 +7601,34 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7638,32 +7638,32 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
@@ -7689,16 +7689,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7710,32 +7710,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
@@ -7761,16 +7761,16 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="O98" s="16" t="n">
         <v>0</v>
@@ -7782,27 +7782,27 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K99" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O99" s="16" t="n">
         <v>0</v>
@@ -7854,32 +7854,32 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
@@ -7905,16 +7905,16 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>1088.5</v>
+        <v>203.5</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7926,32 +7926,32 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7977,16 +7977,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7998,12 +7998,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
@@ -8049,16 +8049,16 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O102" s="16" t="n">
         <v>0</v>
@@ -8070,12 +8070,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
@@ -8121,16 +8121,16 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O103" s="16" t="n">
         <v>0</v>
@@ -8142,12 +8142,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
@@ -8193,16 +8193,16 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O104" s="16" t="n">
         <v>0</v>
@@ -8214,12 +8214,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -8254,27 +8254,27 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K105" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8286,32 +8286,32 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -8321,32 +8321,32 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8358,12 +8358,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -8398,29 +8398,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8430,27 +8430,27 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8477,22 +8477,22 @@
         <v>9</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>3.75</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8502,26 +8502,28 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8540,29 +8542,29 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="12" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O109" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8572,12 +8574,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8587,7 +8589,7 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8605,34 +8607,34 @@
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8642,12 +8644,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8657,13 +8659,11 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v/>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
@@ -8682,27 +8682,27 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O111" s="16" t="n">
         <v>0</v>
@@ -8765,18 +8765,18 @@
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8837,18 +8837,18 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O113" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8909,18 +8909,18 @@
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="15" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -9002,12 +9002,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -9017,11 +9017,13 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -9040,29 +9042,29 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9072,12 +9074,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9087,7 +9089,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9105,32 +9107,32 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O117" s="16" t="n">
         <v>0</v>
@@ -9142,28 +9144,26 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E118" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v/>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
@@ -9193,18 +9193,18 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="15" t="n">
+        <v>460</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9214,12 +9214,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9229,11 +9229,13 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9247,49 +9249,49 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O119" s="16" t="n">
-        <v>418.9</v>
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
-        <v>46.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9299,7 +9301,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9322,54 +9324,54 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.75</v>
+        <v>9</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O120" s="16" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>0</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9387,32 +9389,32 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O121" s="16" t="n">
         <v>0</v>
@@ -9424,12 +9426,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
@@ -9439,7 +9441,7 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9462,29 +9464,29 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="15" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9494,12 +9496,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9509,7 +9511,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9532,23 +9534,23 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>15</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
@@ -9613,12 +9615,12 @@
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
@@ -9649,7 +9651,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9683,12 +9685,12 @@
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9719,7 +9721,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9753,12 +9755,12 @@
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
@@ -9774,22 +9776,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9812,23 +9814,23 @@
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9844,22 +9846,22 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9877,34 +9879,34 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="15" t="n">
@@ -9914,22 +9916,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9952,27 +9954,27 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
         <v>18</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O129" s="16" t="n">
         <v>0</v>
@@ -9984,12 +9986,12 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -9999,7 +10001,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10017,34 +10019,34 @@
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
@@ -10054,12 +10056,12 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10069,7 +10071,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10092,7 +10094,7 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
@@ -10103,12 +10105,12 @@
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10124,12 +10126,12 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
@@ -10139,13 +10141,11 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E132" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="n">
+        <v/>
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
@@ -10154,27 +10154,35 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr"/>
-      <c r="M132" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10188,26 +10196,28 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E133" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
@@ -10226,11 +10236,11 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K133" s="11" t="n">
         <v>0.25</v>
@@ -10250,22 +10260,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10283,7 +10293,7 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
@@ -10295,7 +10305,7 @@
         <v>22</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L134" s="14" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -10312,22 +10322,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10335,44 +10345,36 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M135" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O135" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="12" t="n">
@@ -10382,22 +10384,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10405,7 +10407,7 @@
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
@@ -10415,34 +10417,34 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="15" t="n">
@@ -10452,22 +10454,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10480,7 +10482,7 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -10490,17 +10492,25 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr"/>
-      <c r="M137" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N137" s="12" t="n">
         <v>0</v>
       </c>
@@ -10514,12 +10524,12 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
@@ -10529,7 +10539,7 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10552,14 +10562,14 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10576,22 +10586,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10614,14 +10624,14 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10638,12 +10648,12 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
@@ -10653,7 +10663,7 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10671,19 +10681,19 @@
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10700,12 +10710,12 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10715,7 +10725,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10728,35 +10738,27 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M141" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10770,22 +10772,22 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10798,23 +10800,35 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H142" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H142" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr"/>
-      <c r="M142" s="14" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M142" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10828,12 +10842,12 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
@@ -10843,7 +10857,7 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10859,32 +10873,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H143" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H143" s="11" t="inlineStr"/>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10898,22 +10900,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10926,29 +10928,33 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H144" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1.5</v>
+        <v>6.75</v>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M144" s="14" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N144" s="15" t="n">
@@ -10964,24 +10970,26 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v/>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
@@ -10990,27 +10998,31 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H145" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr"/>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr"/>
-      <c r="M145" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N145" s="12" t="n">
         <v>0</v>
       </c>
@@ -11024,21 +11036,25 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr"/>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E146" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11046,20 +11062,24 @@
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H146" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L146" s="14" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -11076,18 +11096,18 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr"/>
@@ -11104,11 +11124,11 @@
       <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" s="11" t="n">
         <v>0.25</v>
@@ -11128,18 +11148,18 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr"/>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr"/>
@@ -11156,7 +11176,7 @@
       <c r="H148" s="14" t="inlineStr"/>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
@@ -11180,18 +11200,18 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
@@ -11202,35 +11222,27 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M149" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr"/>
       <c r="N149" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O149" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P149" s="12" t="n">
@@ -11240,18 +11252,18 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr"/>
@@ -11262,27 +11274,35 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L150" s="14" t="inlineStr"/>
-      <c r="M150" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M150" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N150" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="O150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="15" t="n">
@@ -11292,18 +11312,18 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr"/>
@@ -11320,14 +11340,14 @@
       <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
@@ -11344,18 +11364,18 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr"/>
@@ -11366,31 +11386,23 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M152" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11404,18 +11416,18 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr"/>
@@ -11432,61 +11444,121 @@
       <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K153" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr"/>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr"/>
+      <c r="F154" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G154" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr"/>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J153" s="11" t="n">
+      <c r="J154" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K153" s="11" t="n">
+      <c r="K154" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L153" s="11" t="inlineStr">
+      <c r="L154" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M153" s="11" t="inlineStr">
+      <c r="M154" s="14" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N153" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="17" t="inlineStr">
+      <c r="N154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B154" s="17" t="inlineStr"/>
-      <c r="C154" s="17" t="inlineStr"/>
-      <c r="D154" s="17" t="inlineStr"/>
-      <c r="E154" s="17" t="inlineStr"/>
-      <c r="F154" s="17" t="inlineStr"/>
-      <c r="G154" s="17" t="inlineStr"/>
-      <c r="H154" s="17" t="inlineStr"/>
-      <c r="I154" s="17" t="inlineStr"/>
-      <c r="J154" s="17" t="inlineStr"/>
-      <c r="K154" s="17" t="inlineStr"/>
-      <c r="L154" s="17" t="inlineStr"/>
-      <c r="M154" s="17" t="inlineStr"/>
-      <c r="N154" s="18" t="n">
+      <c r="B155" s="17" t="inlineStr"/>
+      <c r="C155" s="17" t="inlineStr"/>
+      <c r="D155" s="17" t="inlineStr"/>
+      <c r="E155" s="17" t="inlineStr"/>
+      <c r="F155" s="17" t="inlineStr"/>
+      <c r="G155" s="17" t="inlineStr"/>
+      <c r="H155" s="17" t="inlineStr"/>
+      <c r="I155" s="17" t="inlineStr"/>
+      <c r="J155" s="17" t="inlineStr"/>
+      <c r="K155" s="17" t="inlineStr"/>
+      <c r="L155" s="17" t="inlineStr"/>
+      <c r="M155" s="17" t="inlineStr"/>
+      <c r="N155" s="18" t="n">
         <v>119873.717</v>
       </c>
-      <c r="O154" s="18" t="n">
+      <c r="O155" s="18" t="n">
         <v>7864.200000000001</v>
       </c>
-      <c r="P154" s="18" t="n">
-        <v>47.93</v>
+      <c r="P155" s="18" t="n">
+        <v>46.04</v>
       </c>
     </row>
   </sheetData>
@@ -11641,6 +11713,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12668,7 +12741,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>104</v>
+        <v>109.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>17.5</v>
@@ -12677,7 +12750,7 @@
         <v>5.58</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>127.08</v>
+        <v>132.83</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>11.25</v>
@@ -12687,7 +12760,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -12704,10 +12777,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -12717,7 +12790,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12802,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>57.08</v>
+        <v>57.33</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-15.xlsx
+++ b/jira_export_2026-10-15.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>241 h</t>
+          <t>246 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -4237,7 +4237,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>15.5</v>
+        <v>16.25</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>576</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>37.16</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="50">
@@ -5389,7 +5389,7 @@
         <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>12</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>418.9</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>46.54</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="121">
@@ -11558,7 +11558,7 @@
         <v>7864.200000000001</v>
       </c>
       <c r="P155" s="18" t="n">
-        <v>46.04</v>
+        <v>44.98</v>
       </c>
     </row>
   </sheetData>
@@ -12741,7 +12741,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>109.75</v>
+        <v>113.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>17.5</v>
@@ -12750,17 +12750,17 @@
         <v>5.58</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>132.83</v>
+        <v>136.83</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>57.33</v>
+        <v>57.58</v>
       </c>
     </row>
   </sheetData>
@@ -12890,13 +12890,13 @@
         <v>505748</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>214701</v>
+        <v>211019</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>291047</v>
+        <v>294728</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>229035</v>
+        <v>232716</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16651</v>
@@ -12940,13 +12940,13 @@
         <v>242435</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>145640</v>
+        <v>141958</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>96795</v>
+        <v>100477</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>54107</v>
+        <v>57789</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>7476</v>

--- a/jira_export_2026-10-15.xlsx
+++ b/jira_export_2026-10-15.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>7,864 €</t>
+          <t>10,979 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2,694 €</t>
+          <t>5,808 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>246 h</t>
+          <t>260 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P155"/>
+  <dimension ref="A1:P158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L16" s="14" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         <v>455</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="24">
@@ -3021,7 +3021,7 @@
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="L47" s="11" t="inlineStr"/>
       <c r="M47" s="11" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         <v>2649.6</v>
       </c>
       <c r="O49" s="16" t="n">
-        <v>576</v>
+        <v>1152</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>35.45</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="50">
@@ -4406,69 +4406,61 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M52" s="14" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
       <c r="N52" s="15" t="n">
-        <v>5388.936</v>
-      </c>
-      <c r="O52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
@@ -4478,27 +4470,27 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4518,7 +4510,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4529,16 +4521,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>177.5</v>
+        <v>5388.936</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4550,27 +4542,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4585,12 +4577,12 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4601,16 +4593,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>1700</v>
+        <v>177.5</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4622,27 +4614,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4657,64 +4649,64 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1786.1</v>
+        <v>1700</v>
       </c>
       <c r="O55" s="16" t="n">
-        <v>909.9</v>
+        <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4734,64 +4726,64 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>170</v>
+        <v>1786.1</v>
       </c>
       <c r="O56" s="16" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4801,32 +4793,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4838,27 +4830,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4885,57 +4877,57 @@
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>4.25</v>
+        <v>14.75</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>484</v>
+        <v>3000</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>308</v>
+        <v>1242.9</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>72.47</v>
+        <v>84.26000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4945,64 +4937,64 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>700</v>
-      </c>
-      <c r="O59" s="16" t="n">
-        <v>0</v>
+        <v>484</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>572</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>0</v>
+        <v>134.59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5033,16 +5025,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5054,32 +5046,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5089,32 +5081,32 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>186.235</v>
+        <v>170</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5126,12 +5118,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5141,12 +5133,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5173,20 +5165,20 @@
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>1890</v>
+        <v>186.235</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5198,27 +5190,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5238,27 +5230,27 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>400</v>
+        <v>1890</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5270,12 +5262,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5285,12 +5277,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5310,27 +5302,27 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>552</v>
+        <v>400</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5342,27 +5334,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5389,22 +5381,22 @@
         <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
+        <v>552</v>
+      </c>
+      <c r="O65" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5414,32 +5406,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5454,29 +5446,29 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5486,27 +5478,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5521,32 +5513,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5558,27 +5550,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5609,16 +5601,16 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5630,32 +5622,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5665,12 +5657,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5681,16 +5673,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>171.4</v>
+        <v>203.5</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5702,27 +5694,27 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5753,16 +5745,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>400</v>
+        <v>171.4</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5774,32 +5766,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5809,12 +5801,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5825,16 +5817,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>6177.52</v>
+        <v>400</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5846,27 +5838,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5881,12 +5873,12 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
@@ -5897,16 +5889,16 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>500</v>
+        <v>6177.52</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5918,32 +5910,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5958,29 +5950,29 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O73" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5990,12 +5982,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6005,12 +5997,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6020,7 +6012,7 @@
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H74" s="14" t="inlineStr">
@@ -6030,17 +6022,25 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L74" s="14" t="inlineStr"/>
-      <c r="M74" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L74" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33315</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>00167138</t>
+        </is>
+      </c>
       <c r="N74" s="15" t="n">
         <v>0</v>
       </c>
@@ -6054,37 +6054,37 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -6094,29 +6094,21 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M75" s="11" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr"/>
       <c r="N75" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6126,27 +6118,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6161,12 +6153,12 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6177,16 +6169,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6198,32 +6190,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6233,32 +6225,32 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>337.5</v>
+        <v>149</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6317,20 +6309,20 @@
         <v>5</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>320</v>
+        <v>337.5</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6342,32 +6334,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6377,35 +6369,35 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
-        <v>1047</v>
+        <v>320</v>
+      </c>
+      <c r="O79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6414,32 +6406,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6449,35 +6441,35 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="O80" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
+        <v>1047</v>
       </c>
       <c r="P80" s="15" t="n">
         <v>0</v>
@@ -6486,32 +6478,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6521,7 +6513,7 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -6533,20 +6525,20 @@
         <v>6</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6558,32 +6550,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6593,34 +6585,34 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6630,32 +6622,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6665,7 +6657,7 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -6677,22 +6669,22 @@
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>680.8</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6702,12 +6694,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6717,12 +6709,12 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6737,12 +6729,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6753,16 +6745,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6774,32 +6766,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6809,12 +6801,12 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6825,16 +6817,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>403.074</v>
+        <v>2614.5</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6846,32 +6838,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6881,7 +6873,7 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
@@ -6897,19 +6889,19 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
-        <v>276</v>
+        <v>403.074</v>
+      </c>
+      <c r="O86" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
         <v>0</v>
@@ -6918,32 +6910,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6953,12 +6945,12 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
@@ -6969,19 +6961,19 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O87" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>276</v>
       </c>
       <c r="P87" s="12" t="n">
         <v>0</v>
@@ -6990,32 +6982,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7025,32 +7017,32 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K88" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>11278.05</v>
+        <v>142.1</v>
       </c>
       <c r="O88" s="16" t="n">
         <v>0</v>
@@ -7062,32 +7054,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7097,12 +7089,12 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7113,16 +7105,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>1000</v>
+        <v>11278.05</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7134,32 +7126,32 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -7169,7 +7161,7 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
@@ -7185,16 +7177,16 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="O90" s="16" t="n">
         <v>0</v>
@@ -7206,12 +7198,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7221,12 +7213,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7246,7 +7238,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
@@ -7257,16 +7249,16 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7278,32 +7270,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7313,32 +7305,32 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O92" s="16" t="n">
         <v>0</v>
@@ -7350,32 +7342,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7385,32 +7377,32 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>3240</v>
+        <v>910</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7422,27 +7414,27 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
@@ -7462,7 +7454,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
@@ -7473,16 +7465,16 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>1050</v>
+        <v>4050</v>
       </c>
       <c r="O94" s="16" t="n">
         <v>0</v>
@@ -7494,27 +7486,27 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7534,7 +7526,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7545,16 +7537,16 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7566,32 +7558,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7601,34 +7593,34 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7638,32 +7630,32 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7673,34 +7665,34 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7710,32 +7702,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7750,7 +7742,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
@@ -7761,16 +7753,16 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O98" s="16" t="n">
         <v>0</v>
@@ -7782,32 +7774,32 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -7817,12 +7809,12 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
@@ -7833,16 +7825,16 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="O99" s="16" t="n">
         <v>0</v>
@@ -7854,27 +7846,27 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -7889,32 +7881,32 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K100" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7926,32 +7918,32 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -7961,12 +7953,12 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7977,16 +7969,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1088.5</v>
+        <v>203.5</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7998,32 +7990,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8033,12 +8025,12 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
@@ -8049,16 +8041,16 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O102" s="16" t="n">
         <v>0</v>
@@ -8070,12 +8062,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8085,7 +8077,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -8110,7 +8102,7 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
@@ -8121,16 +8113,16 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O103" s="16" t="n">
         <v>0</v>
@@ -8142,12 +8134,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8157,12 +8149,12 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -8182,7 +8174,7 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
@@ -8193,16 +8185,16 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O104" s="16" t="n">
         <v>0</v>
@@ -8214,12 +8206,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8229,12 +8221,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -8254,7 +8246,7 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
@@ -8265,16 +8257,16 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8286,12 +8278,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8301,12 +8293,12 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -8326,27 +8318,27 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K106" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8358,32 +8350,32 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8393,32 +8385,32 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8430,12 +8422,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8445,12 +8437,12 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8470,29 +8462,29 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8502,27 +8494,27 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -8549,22 +8541,22 @@
         <v>9</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>3.75</v>
+        <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8574,26 +8566,28 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E110" s="14" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -8612,29 +8606,29 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8644,12 +8638,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8659,7 +8653,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8677,34 +8671,34 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8714,12 +8708,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8729,13 +8723,11 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v/>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -8754,27 +8746,27 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O112" s="16" t="n">
         <v>0</v>
@@ -8833,22 +8825,22 @@
         <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O113" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8905,22 +8897,22 @@
         <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8977,26 +8969,26 @@
         <v>11</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
-        <v>0</v>
+        <v>1790</v>
+      </c>
+      <c r="O115" s="16" t="n">
+        <v>895</v>
       </c>
       <c r="P115" s="12" t="n">
-        <v>0</v>
+        <v>639.29</v>
       </c>
     </row>
     <row r="116">
@@ -9049,16 +9041,16 @@
         <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9074,12 +9066,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9089,11 +9081,13 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9112,29 +9106,29 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.25</v>
+        <v>1.4</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O117" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9144,12 +9138,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9159,7 +9153,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9177,32 +9171,32 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O118" s="16" t="n">
         <v>0</v>
@@ -9214,28 +9208,26 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v/>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9249,12 +9241,12 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
@@ -9265,18 +9257,18 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="O119" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9286,12 +9278,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9301,11 +9293,13 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
@@ -9319,49 +9313,49 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>10.25</v>
+        <v>0.5</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O120" s="16" t="n">
-        <v>418.9</v>
+        <v>0</v>
+      </c>
+      <c r="O120" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>40.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9371,7 +9365,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9394,54 +9388,54 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.75</v>
+        <v>10.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O121" s="16" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P121" s="12" t="n">
-        <v>0</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9459,32 +9453,32 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O122" s="16" t="n">
         <v>0</v>
@@ -9496,12 +9490,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9511,7 +9505,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9534,29 +9528,29 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="12" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O123" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9566,12 +9560,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9581,7 +9575,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9604,23 +9598,23 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>15</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
@@ -9685,12 +9679,12 @@
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
@@ -9721,7 +9715,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9755,12 +9749,12 @@
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
@@ -9791,7 +9785,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9825,12 +9819,12 @@
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9846,22 +9840,22 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9884,23 +9878,23 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
@@ -9916,22 +9910,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9954,29 +9948,29 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O129" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
@@ -9986,12 +9980,12 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -10001,7 +9995,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10019,34 +10013,34 @@
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
@@ -10056,22 +10050,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10089,34 +10083,34 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O131" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="12" t="n">
@@ -10126,12 +10120,12 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
@@ -10141,7 +10135,7 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10159,34 +10153,34 @@
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O132" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="15" t="n">
@@ -10196,12 +10190,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10211,13 +10205,11 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v/>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
@@ -10226,27 +10218,35 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr"/>
-      <c r="M133" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N133" s="12" t="n">
         <v>0</v>
       </c>
@@ -10260,22 +10260,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10288,27 +10288,35 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr"/>
-      <c r="M134" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M134" s="14" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N134" s="15" t="n">
         <v>0</v>
       </c>
@@ -10322,12 +10330,12 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10337,11 +10345,13 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
@@ -10355,19 +10365,19 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="11" t="inlineStr"/>
       <c r="M135" s="11" t="inlineStr"/>
@@ -10384,22 +10394,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10407,44 +10417,36 @@
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M136" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
       <c r="N136" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="15" t="n">
@@ -10454,12 +10456,12 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -10469,7 +10471,7 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10482,35 +10484,27 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
         <v>0</v>
       </c>
@@ -10524,22 +10518,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10547,36 +10541,44 @@
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" s="14" t="inlineStr"/>
-      <c r="M138" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L138" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M138" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N138" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O138" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="15" t="n">
@@ -10586,22 +10588,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10614,7 +10616,7 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -10624,17 +10626,25 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K139" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10648,22 +10658,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10686,14 +10696,14 @@
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10710,22 +10720,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10743,19 +10753,19 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L141" s="11" t="inlineStr"/>
       <c r="M141" s="11" t="inlineStr"/>
@@ -10772,12 +10782,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10787,7 +10797,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10800,7 +10810,7 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
@@ -10810,25 +10820,17 @@
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10842,22 +10844,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10873,17 +10875,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H143" s="11" t="inlineStr"/>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="L143" s="11" t="inlineStr"/>
       <c r="M143" s="11" t="inlineStr"/>
@@ -10900,22 +10906,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10928,33 +10934,33 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>6.75</v>
+        <v>1.25</v>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M144" s="14" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N144" s="15" t="n">
@@ -10970,22 +10976,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -10998,31 +11004,23 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr"/>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="12" t="n">
         <v>0</v>
       </c>
@@ -11036,24 +11034,26 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C146" s="14" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E146" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="n">
+        <v/>
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
@@ -11072,17 +11072,25 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr"/>
-      <c r="M146" s="14" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M146" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N146" s="15" t="n">
         <v>0</v>
       </c>
@@ -11096,21 +11104,27 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="C147" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v/>
+      </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11118,23 +11132,31 @@
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr"/>
-      <c r="M147" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N147" s="12" t="n">
         <v>0</v>
       </c>
@@ -11148,21 +11170,25 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr"/>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
-        </is>
-      </c>
-      <c r="E148" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F148" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11170,20 +11196,24 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H148" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -11200,18 +11230,18 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
@@ -11228,11 +11258,11 @@
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" s="11" t="n">
         <v>0.25</v>
@@ -11252,18 +11282,18 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr"/>
@@ -11274,35 +11304,27 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M150" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
       <c r="N150" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O150" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="15" t="n">
@@ -11312,18 +11334,18 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr"/>
@@ -11340,11 +11362,11 @@
       <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K151" s="11" t="n">
         <v>0.25</v>
@@ -11364,18 +11386,18 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr"/>
@@ -11386,27 +11408,35 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr"/>
-      <c r="M152" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N152" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="O152" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="15" t="n">
@@ -11416,18 +11446,18 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr"/>
@@ -11438,31 +11468,23 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11476,18 +11498,18 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr"/>
@@ -11498,67 +11520,231 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L154" s="14" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+      <c r="N154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1288</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr"/>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr"/>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr"/>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J155" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K155" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
+      <c r="N155" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr"/>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr"/>
+      <c r="F156" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G156" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr"/>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K156" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N156" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr"/>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr"/>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr"/>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J154" s="14" t="n">
+      <c r="J157" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K154" s="14" t="n">
+      <c r="K157" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L154" s="14" t="inlineStr">
+      <c r="L157" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M154" s="14" t="inlineStr">
+      <c r="M157" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N154" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="17" t="inlineStr">
+      <c r="N157" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" s="17" t="inlineStr"/>
-      <c r="C155" s="17" t="inlineStr"/>
-      <c r="D155" s="17" t="inlineStr"/>
-      <c r="E155" s="17" t="inlineStr"/>
-      <c r="F155" s="17" t="inlineStr"/>
-      <c r="G155" s="17" t="inlineStr"/>
-      <c r="H155" s="17" t="inlineStr"/>
-      <c r="I155" s="17" t="inlineStr"/>
-      <c r="J155" s="17" t="inlineStr"/>
-      <c r="K155" s="17" t="inlineStr"/>
-      <c r="L155" s="17" t="inlineStr"/>
-      <c r="M155" s="17" t="inlineStr"/>
-      <c r="N155" s="18" t="n">
-        <v>119873.717</v>
-      </c>
-      <c r="O155" s="18" t="n">
-        <v>7864.200000000001</v>
-      </c>
-      <c r="P155" s="18" t="n">
-        <v>44.98</v>
+      <c r="B158" s="17" t="inlineStr"/>
+      <c r="C158" s="17" t="inlineStr"/>
+      <c r="D158" s="17" t="inlineStr"/>
+      <c r="E158" s="17" t="inlineStr"/>
+      <c r="F158" s="17" t="inlineStr"/>
+      <c r="G158" s="17" t="inlineStr"/>
+      <c r="H158" s="17" t="inlineStr"/>
+      <c r="I158" s="17" t="inlineStr"/>
+      <c r="J158" s="17" t="inlineStr"/>
+      <c r="K158" s="17" t="inlineStr"/>
+      <c r="L158" s="17" t="inlineStr"/>
+      <c r="M158" s="17" t="inlineStr"/>
+      <c r="N158" s="18" t="n">
+        <v>120683.717</v>
+      </c>
+      <c r="O158" s="18" t="n">
+        <v>10978.6</v>
+      </c>
+      <c r="P158" s="18" t="n">
+        <v>58.61</v>
       </c>
     </row>
   </sheetData>
@@ -11714,6 +11900,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12741,16 +12930,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>113.75</v>
+        <v>119.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5.58</v>
+        <v>6.58</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>136.83</v>
+        <v>144.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>11.75</v>
@@ -12760,7 +12949,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.4%</t>
         </is>
       </c>
     </row>
@@ -12771,16 +12960,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>29.75</v>
+        <v>32.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>8.25</v>
+        <v>10.25</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -12790,7 +12979,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12991,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>57.58</v>
+        <v>59.33</v>
       </c>
     </row>
   </sheetData>
@@ -12887,16 +13076,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>505748</v>
+        <v>502633</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>211019</v>
+        <v>210619</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>294728</v>
+        <v>292015</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>232716</v>
+        <v>230002</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16651</v>
@@ -12912,16 +13101,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>260213</v>
+        <v>257098</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>65961</v>
+        <v>65561</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>194252</v>
+        <v>191538</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>174927</v>
+        <v>172214</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -12966,7 +13155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12990,7 +13179,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 22 commande(s)</t>
+          <t>Épics créées ce mois — 23 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13045,22 +13234,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36459</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36453</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t xml:space="preserve">COMMUNE DE EVREUX </t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -13070,7 +13259,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -13080,22 +13269,22 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00184982</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -13105,7 +13294,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -13115,7 +13304,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -13125,32 +13314,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>985</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36387</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36381</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRIANCON</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -13160,7 +13349,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -13170,22 +13359,22 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00184667</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36376</t>
+          <t>PDMDEP-36387</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36370</t>
+          <t>PDMDEP-36381</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -13195,7 +13384,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE DE BRIANCON</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -13205,7 +13394,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -13215,7 +13404,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00184665</t>
+          <t>00184667</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
@@ -13225,22 +13414,22 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36349</t>
+          <t>PDMDEP-36376</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36345</t>
+          <t>PDMDEP-36370</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LEUCATE Service Achat</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -13260,7 +13449,7 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00184482</t>
+          <t>00184665</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
@@ -13270,22 +13459,22 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36335</t>
+          <t>PDMDEP-36349</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-36345</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t>MAIRIE DE LEUCATE Service Achat</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -13305,7 +13494,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00184406</t>
+          <t>00184482</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
@@ -13315,22 +13504,22 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36335</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -13340,7 +13529,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -13350,42 +13539,42 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00184406</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36439</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36435</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANGERS</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -13395,11 +13584,11 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00184863</t>
+          <t>00183814</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
@@ -13941,22 +14130,22 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36256</t>
+          <t>PDMDEP-36439</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36247</t>
+          <t>PDMDEP-36435</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AVIGNON</t>
+          <t>COMMUNE D'ANGERS</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -13966,7 +14155,7 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -13976,7 +14165,7 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>00184863</t>
         </is>
       </c>
       <c r="I25" s="25" t="n">
@@ -13986,73 +14175,97 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36256</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I27" s="25" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>22 commande(s)</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="n">
-        <v>13313</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B28" s="17" t="n"/>
@@ -14063,17 +14276,17 @@
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>15 commande(s)</t>
+          <t>23 commande(s)</t>
         </is>
       </c>
       <c r="I28" s="24" t="n">
-        <v>8028</v>
+        <v>13313</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B29" s="17" t="n"/>
@@ -14084,10 +14297,31 @@
       <c r="G29" s="17" t="n"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>7 commande(s)</t>
+          <t>15 commande(s)</t>
         </is>
       </c>
       <c r="I29" s="24" t="n">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="n">
         <v>5285</v>
       </c>
     </row>
